--- a/output/pdf_financials_xlsx/PPP.xlsx
+++ b/output/pdf_financials_xlsx/PPP.xlsx
@@ -5962,19 +5962,19 @@
         <v>0</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>7.871449</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>8.464428</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>8.758936</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>9.321903000000001</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>9.904666000000001</v>
       </c>
     </row>
     <row r="93">
@@ -9846,7 +9846,11 @@
           <t>Reserves 6</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>-</t>
@@ -11236,7 +11240,11 @@
           <t>Reserves 7</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/PPP.xlsx
+++ b/output/pdf_financials_xlsx/PPP.xlsx
@@ -1029,55 +1029,55 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.047593</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.00654</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.015846</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.140499</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.144521</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.105852</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.097996</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.069703</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.058329</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.068869</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.102387</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.1116</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.024284</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.034933</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.030434</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.074216</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>0.139264</v>
       </c>
     </row>
     <row r="13">
@@ -1975,55 +1975,55 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.07720399999999999</v>
+        <v>-0.124797</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.238556</v>
+        <v>-0.245096</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.662136</v>
+        <v>-1.677982</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-7.509874</v>
+        <v>-7.650373</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-8.284528999999999</v>
+        <v>-8.42905</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.898369</v>
+        <v>-1.004221</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.426836</v>
+        <v>-0.524832</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-0.554949</v>
+        <v>-0.624652</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-0.699533</v>
+        <v>-0.757862</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-0.62963</v>
+        <v>-0.698499</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-1.220911</v>
+        <v>-1.323298</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-6.396501</v>
+        <v>-6.508101</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-5.516416</v>
+        <v>-5.5407</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-7.567819</v>
+        <v>-7.602752</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-4.307735</v>
+        <v>-4.338169</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-6.860957</v>
+        <v>-6.935173</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>-5.215301</v>
+        <v>-5.354565</v>
       </c>
     </row>
     <row r="28">
@@ -2091,55 +2091,55 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.07720399999999999</v>
+        <v>-0.124797</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.238556</v>
+        <v>-0.245096</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.662136</v>
+        <v>-1.677982</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-7.509874</v>
+        <v>-7.650373</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-8.284528999999999</v>
+        <v>-8.42905</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.898369</v>
+        <v>-1.004221</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.426836</v>
+        <v>-0.524832</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.554949</v>
+        <v>-0.624652</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-0.699533</v>
+        <v>-0.757862</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-0.62963</v>
+        <v>-0.698499</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-1.220911</v>
+        <v>-1.323298</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-6.396501</v>
+        <v>-6.508101</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-5.516416</v>
+        <v>-5.5407</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-7.567819</v>
+        <v>-7.602752</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-4.307735</v>
+        <v>-4.338169</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-6.860957</v>
+        <v>-6.935173</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-5.215301</v>
+        <v>-5.354565</v>
       </c>
     </row>
     <row r="30">
@@ -2434,7 +2434,7 @@
         <v>3.009935</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>3.558391</v>
       </c>
       <c r="O34" s="3" t="n">
         <v>0.887341</v>
@@ -2550,7 +2550,7 @@
         <v>3.009935</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>3.558391</v>
       </c>
       <c r="O36" s="3" t="n">
         <v>0.887341</v>
@@ -3246,7 +3246,7 @@
         <v>0.611591</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>7.012288</v>
+        <v>3.453897</v>
       </c>
       <c r="O48" s="3" t="n">
         <v>2.110101</v>
@@ -11343,7 +11343,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -33527,7 +33527,7 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
@@ -39463,7 +39463,7 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
@@ -42154,7 +42154,7 @@
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
@@ -49259,7 +49259,7 @@
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E414" s="5" t="n">

--- a/output/pdf_financials_xlsx/PPP.xlsx
+++ b/output/pdf_financials_xlsx/PPP.xlsx
@@ -7010,10 +7010,10 @@
         <v>0</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>0</v>
+        <v>-0.051048</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>0</v>
+        <v>-0.001325</v>
       </c>
       <c r="G111" s="3" t="n">
         <v>0</v>
@@ -7269,16 +7269,16 @@
         <v>0</v>
       </c>
       <c r="N115" s="3" t="n">
-        <v>0</v>
+        <v>0.558517</v>
       </c>
       <c r="O115" s="3" t="n">
-        <v>0</v>
+        <v>0.6025239999999999</v>
       </c>
       <c r="P115" s="3" t="n">
-        <v>0</v>
+        <v>1.899482</v>
       </c>
       <c r="Q115" s="3" t="n">
-        <v>0</v>
+        <v>0.06542100000000001</v>
       </c>
       <c r="R115" s="3" t="n">
         <v>0</v>
@@ -8388,10 +8388,10 @@
         <v>0</v>
       </c>
       <c r="E134" s="3" t="n">
-        <v>0</v>
+        <v>-0.051048</v>
       </c>
       <c r="F134" s="3" t="n">
-        <v>0</v>
+        <v>-0.001325</v>
       </c>
       <c r="G134" s="3" t="n">
         <v>0</v>
@@ -8450,10 +8450,10 @@
         <v>-0.344739</v>
       </c>
       <c r="E135" s="3" t="n">
-        <v>-1.46126</v>
+        <v>-1.512308</v>
       </c>
       <c r="F135" s="3" t="n">
-        <v>-0.794686</v>
+        <v>-0.796011</v>
       </c>
       <c r="G135" s="3" t="n">
         <v>-0.5581120000000001</v>
@@ -18728,7 +18728,11 @@
           <t>Proceeds on sale of investments 5</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr"/>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E105" t="inlineStr">
         <is>
           <t>-</t>
@@ -20914,7 +20918,11 @@
           <t>Proceeds on sale of investments 6</t>
         </is>
       </c>
-      <c r="D127" t="inlineStr"/>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E127" t="inlineStr">
         <is>
           <t>-</t>
@@ -22126,7 +22134,11 @@
           <t>Proceeds from private placement 7</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr"/>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E139" t="inlineStr">
         <is>
           <t>-</t>
@@ -28475,7 +28487,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D204" t="inlineStr"/>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E204" t="inlineStr">
         <is>
           <t>-</t>
@@ -31871,7 +31887,11 @@
           <t>Common shares issued for cash</t>
         </is>
       </c>
-      <c r="D238" t="inlineStr"/>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E238" t="inlineStr">
         <is>
           <t>-</t>
